--- a/2sem/electro/lab1/sheet1.xlsx
+++ b/2sem/electro/lab1/sheet1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclitt\Documents\nstu\2sem\electro\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265E9958-AE9A-4CBF-B196-99CE2BFD0FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8520BCE2-BFFF-4C89-A3C1-20FED9E2630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
